--- a/docs/ทะเบียนกลาง.xlsx
+++ b/docs/ทะเบียนกลาง.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +61,29 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +125,26 @@
         <fgColor rgb="00E1F5FE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -252,10 +293,78 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="007F7F7F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+          <bgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -758,7 +867,7 @@
           <t>RegisterScreen.png</t>
         </is>
       </c>
-      <c r="L2" s="31" t="inlineStr">
+      <c r="L2" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -821,7 +930,7 @@
           <t>RegisterScreen.png</t>
         </is>
       </c>
-      <c r="L3" s="31" t="inlineStr">
+      <c r="L3" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -880,7 +989,7 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="31" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -947,7 +1056,7 @@
           <t>RegisterScreen.png</t>
         </is>
       </c>
-      <c r="L5" s="31" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1014,7 +1123,7 @@
           <t>OnboardingScreen.png</t>
         </is>
       </c>
-      <c r="L6" s="31" t="inlineStr">
+      <c r="L6" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1081,7 +1190,7 @@
           <t>LoginScreen.png</t>
         </is>
       </c>
-      <c r="L7" s="31" t="inlineStr">
+      <c r="L7" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1144,7 +1253,7 @@
           <t>ProfileScreen.png</t>
         </is>
       </c>
-      <c r="L8" s="31" t="inlineStr">
+      <c r="L8" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1207,7 +1316,7 @@
           <t>LoginScreen.png</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
+      <c r="L9" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1274,7 +1383,7 @@
           <t>ForgotPasswordScreen.png</t>
         </is>
       </c>
-      <c r="L10" s="31" t="inlineStr">
+      <c r="L10" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1337,7 +1446,7 @@
           <t>ForgotPasswordScreen.png</t>
         </is>
       </c>
-      <c r="L11" s="31" t="inlineStr">
+      <c r="L11" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1404,7 +1513,7 @@
           <t>ResetPasswordScreen.png</t>
         </is>
       </c>
-      <c r="L12" s="31" t="inlineStr">
+      <c r="L12" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1463,7 +1572,7 @@
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="31" t="inlineStr">
+      <c r="L13" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1530,7 +1639,7 @@
           <t>ChangePasswordScreen.png</t>
         </is>
       </c>
-      <c r="L14" s="31" t="inlineStr">
+      <c r="L14" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1597,7 +1706,7 @@
           <t>ProfileScreen.png</t>
         </is>
       </c>
-      <c r="L15" s="31" t="inlineStr">
+      <c r="L15" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1660,7 +1769,7 @@
           <t>EditProfileScreen.png</t>
         </is>
       </c>
-      <c r="L16" s="31" t="inlineStr">
+      <c r="L16" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1723,7 +1832,7 @@
           <t>SellerEditStoreScreen.png</t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr">
+      <c r="L17" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1786,7 +1895,7 @@
           <t>SellerEditStoreScreen.png</t>
         </is>
       </c>
-      <c r="L18" s="31" t="inlineStr">
+      <c r="L18" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1849,7 +1958,7 @@
           <t>PickLocationScreen.png</t>
         </is>
       </c>
-      <c r="L19" s="31" t="inlineStr">
+      <c r="L19" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1916,7 +2025,7 @@
           <t>SellerStoreScreen.png</t>
         </is>
       </c>
-      <c r="L20" s="31" t="inlineStr">
+      <c r="L20" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -1979,7 +2088,7 @@
           <t>SellerFoodFormScreen.png</t>
         </is>
       </c>
-      <c r="L21" s="31" t="inlineStr">
+      <c r="L21" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2042,7 +2151,7 @@
           <t>SellerFoodListScreen.png</t>
         </is>
       </c>
-      <c r="L22" s="31" t="inlineStr">
+      <c r="L22" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2105,7 +2214,7 @@
           <t>SellerPostFormScreen.png</t>
         </is>
       </c>
-      <c r="L23" s="31" t="inlineStr">
+      <c r="L23" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2168,7 +2277,7 @@
           <t>SellerPostFormScreen.png</t>
         </is>
       </c>
-      <c r="L24" s="31" t="inlineStr">
+      <c r="L24" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2231,7 +2340,7 @@
           <t>SellerPostFormScreen.png</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L25" s="45" t="inlineStr">
         <is>
           <t>ทำได้บางส่วน</t>
         </is>
@@ -2298,7 +2407,7 @@
           <t>SellerPostListScreen.png</t>
         </is>
       </c>
-      <c r="L26" s="31" t="inlineStr">
+      <c r="L26" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2361,7 +2470,7 @@
           <t>SellerDashboardScreen.png</t>
         </is>
       </c>
-      <c r="L27" s="31" t="inlineStr">
+      <c r="L27" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2424,7 +2533,7 @@
           <t>HomeScreen.png</t>
         </is>
       </c>
-      <c r="L28" s="31" t="inlineStr">
+      <c r="L28" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2487,7 +2596,7 @@
           <t>PostDetailScreen.png</t>
         </is>
       </c>
-      <c r="L29" s="31" t="inlineStr">
+      <c r="L29" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2550,7 +2659,7 @@
           <t>SearchScreen.png</t>
         </is>
       </c>
-      <c r="L30" s="31" t="inlineStr">
+      <c r="L30" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2613,7 +2722,7 @@
           <t>FilterScreen.png</t>
         </is>
       </c>
-      <c r="L31" s="31" t="inlineStr">
+      <c r="L31" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2676,7 +2785,7 @@
           <t>MapScreen.png</t>
         </is>
       </c>
-      <c r="L32" s="31" t="inlineStr">
+      <c r="L32" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2739,7 +2848,7 @@
           <t>StoreLocationScreen.png</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="45" t="inlineStr">
         <is>
           <t>ทำได้บางส่วน</t>
         </is>
@@ -2806,7 +2915,7 @@
           <t>StoreDetailScreen.png</t>
         </is>
       </c>
-      <c r="L34" s="31" t="inlineStr">
+      <c r="L34" s="44" t="inlineStr">
         <is>
           <t>ทำได้</t>
         </is>
@@ -2869,7 +2978,7 @@
           <t>StoreDetailScreen.png</t>
         </is>
       </c>
-      <c r="L35" s="32" t="inlineStr">
+      <c r="L35" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -2932,7 +3041,7 @@
           <t>FavoriteStoresScreen.png</t>
         </is>
       </c>
-      <c r="L36" s="32" t="inlineStr">
+      <c r="L36" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -2995,12 +3104,16 @@
           <t>ReservationConfirmScreen.png</t>
         </is>
       </c>
-      <c r="L37" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M37" s="12" t="inlineStr"/>
+      <c r="L37" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 จองสาคูไส้ไก่ จำนวนคงเหลือลดจาก 13 ชุด เหลือ 10 ชุด ทันทีหลังจอง หลักฐาน สไลด์ UAT-006</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -3054,7 +3167,7 @@
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr"/>
-      <c r="L38" s="32" t="inlineStr">
+      <c r="L38" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -3117,12 +3230,16 @@
           <t>ReservationSuccessScreen.png</t>
         </is>
       </c>
-      <c r="L39" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M39" s="12" t="inlineStr"/>
+      <c r="L39" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าจอยืนยันการจองแสดง QR code พร้อมรหัสรับอาหาร 4 หลัก หลักฐาน สไลด์ UAT-006</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -3180,7 +3297,7 @@
           <t>ReservationConfirmScreen.png</t>
         </is>
       </c>
-      <c r="L40" s="32" t="inlineStr">
+      <c r="L40" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -3247,12 +3364,16 @@
           <t>ReservationDetailScreen.png</t>
         </is>
       </c>
-      <c r="L41" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M41" s="12" t="inlineStr"/>
+      <c r="L41" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าการจองแสดงรายการพร้อมสถานะและเวลาที่เหลือ หลักฐาน สไลด์ UAT-006 UAT-007 UAT-008</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -3310,12 +3431,16 @@
           <t>ReservationDetailScreen.png</t>
         </is>
       </c>
-      <c r="L42" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M42" s="12" t="inlineStr"/>
+      <c r="L42" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 บัวลอย 5 ชุด จอง 2 ชุด เหลือ 3 ชุด กดยกเลิกแล้วกลับมาเป็น 5 ชุด และน้ำลำไยขึ้นสถานะ ยกเลิก คืนจาก 5 เป็น 6 ชุด หลักฐาน สไลด์ UAT-008</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -3369,14 +3494,14 @@
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr"/>
-      <c r="L43" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L43" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>งานวิ่งทุก 5 นาที คิวจึงปิดช้ากว่าเวลาจริงได้สูงสุด 5 นาที</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ขนมปังไส้ทะลัก จอง 2 ชุด จาก 22 เหลือ 20 ชุด เมื่อเลยเวลารับ รายการเปลี่ยนเป็น หมดอายุ และคืนจำนวนกลับเป็น 22 ชุดอัตโนมัติ หลักฐาน สไลด์ UAT-016 งานวิ่งทุก 5 นาที คิวจึงปิดช้ากว่าเวลาจริงได้สูงสุด 5 นาที</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3561,16 @@
           <t>SellerReservationListScreen.png</t>
         </is>
       </c>
-      <c r="L44" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="L44" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าหลักร้านค้าแสดงจำนวนรายการรอรับ และแท็บรายการจองของร้านแสดงคิวที่ลูกค้าจองเข้ามา หลักฐาน สไลด์ UAT-017</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -3499,14 +3628,14 @@
           <t>ScanQrScreen.png</t>
         </is>
       </c>
-      <c r="L45" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L45" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>กรอกรหัสเป็นทางสำรองเมื่อกล้องใช้ไม่ได้</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ร้านกรอกรหัส 4 หลัก 4909 ที่ลูกค้าแสดง ระบบยืนยันสำเร็จ รายการข้าวกะเพราหมูกรอบเปลี่ยนเป็น รับอาหารแล้ว ทั้งฝั่งร้านและฝั่งลูกค้า หลักฐาน สไลด์ UAT-014 กรอกรหัสเป็นทางสำรองเมื่อกล้องใช้ไม่ได้</t>
         </is>
       </c>
     </row>
@@ -3566,14 +3695,14 @@
           <t>ScanQrScreen.png</t>
         </is>
       </c>
-      <c r="L46" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L46" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
         </is>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
-          <t>เคสเชิงลบ</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 เคสเชิงลบ กรอกรหัส 4909 ซ้ำอีกครั้ง ระบบปฏิเสธและแสดงข้อความ ยืนยันไม่สำเร็จ ไม่พบการจองนี้ในระบบ หลักฐาน สไลด์ UAT-015</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3762,16 @@
           <t>WriteReviewScreen.png</t>
         </is>
       </c>
-      <c r="L47" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M47" s="12" t="inlineStr"/>
+      <c r="L47" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 รายการจองเค้กและข้าวกะเพราหมูกรอบขึ้นสถานะ รับอาหารแล้ว จึงมีปุ่มเขียนรีวิว ส่งคะแนน 5 ดาวพร้อมข้อความสำเร็จ หลักฐาน สไลด์ UAT-009</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -3696,14 +3829,14 @@
           <t>WriteReviewScreen.png</t>
         </is>
       </c>
-      <c r="L48" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L48" s="45" t="inlineStr">
+        <is>
+          <t>ทำได้บางส่วน</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
-          <t>เคสเชิงลบ</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ปุ่มเขียนรีวิวขึ้นเฉพาะรายการที่มีสถานะ รับอาหารแล้ว เท่านั้น แต่ยังไม่ได้ทดสอบการกดรีวิวซ้ำในรายการเดิม</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3896,16 @@
           <t>StoreDetailScreen.png</t>
         </is>
       </c>
-      <c r="L49" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M49" s="12" t="inlineStr"/>
+      <c r="L49" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หลังส่งรีวิว คะแนนเฉลี่ยของร้านแสดง 4.7 จาก 3 รีวิว หลักฐาน สไลด์ UAT-009</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
@@ -3826,12 +3963,16 @@
           <t>MyReviewsScreen.png</t>
         </is>
       </c>
-      <c r="L50" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="inlineStr"/>
+      <c r="L50" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 รีวิวปรากฏทั้งฝั่งผู้ใช้และฝั่งหน้าร้านค้า หลักฐาน สไลด์ UAT-009</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -3889,12 +4030,16 @@
           <t>NotificationScreen.png</t>
         </is>
       </c>
-      <c r="L51" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M51" s="12" t="inlineStr"/>
+      <c r="L51" s="45" t="inlineStr">
+        <is>
+          <t>ทำได้บางส่วน</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าแจ้งเตือนแสดงรายการได้ครบทุกบทบาท แต่ยังไม่ได้ทดสอบการทำเครื่องหมายอ่านแล้วและการลบ</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -3952,12 +4097,16 @@
           <t>HomeScreen.png</t>
         </is>
       </c>
-      <c r="L52" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M52" s="12" t="inlineStr"/>
+      <c r="L52" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M52" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หลังลูกค้าจอง ระบบขึ้นจุดแดงบนกระดิ่งของร้าน หลักฐาน สไลด์ UAT-012</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -4015,12 +4164,16 @@
           <t>NotificationScreen.png</t>
         </is>
       </c>
-      <c r="L53" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M53" s="12" t="inlineStr"/>
+      <c r="L53" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M53" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 จองใหม่ขึ้นข้อความ มีการจองใหม่ พร้อมชื่ออาหาร และเมื่อลูกค้ายกเลิกครัวซองต์เนยสด ร้านได้รับข้อความ ลูกค้ายกเลิกการจอง หลักฐาน สไลด์ UAT-012 UAT-013</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -4078,12 +4231,16 @@
           <t>NotificationScreen.png</t>
         </is>
       </c>
-      <c r="L54" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M54" s="12" t="inlineStr"/>
+      <c r="L54" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M54" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ระบบส่งข้อความ ใกล้หมดเวลารับอาหาร เหลืออีกประมาณ 11 นาที ให้เอง และเมื่อเลยเวลาจริงส่ง การจองหมดอายุ หลักฐาน สไลด์ UAT-007</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -4141,12 +4298,16 @@
           <t>ReportScreen.png</t>
         </is>
       </c>
-      <c r="L55" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M55" s="12" t="inlineStr"/>
+      <c r="L55" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ลูกค้าส่งเรื่องเกี่ยวกับร้านครัวคุณแม่พร้อมข้อความและรูปหลักฐาน หลักฐาน สไลด์ UAT-020</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -4204,12 +4365,16 @@
           <t>MyReportsScreen.png</t>
         </is>
       </c>
-      <c r="L56" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M56" s="12" t="inlineStr"/>
+      <c r="L56" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M56" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าการแจ้งปัญหาแสดงเรื่องที่แจ้งพร้อมสถานะ หลักฐาน สไลด์ UAT-020</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -4267,14 +4432,14 @@
           <t>ReportDetailScreen.png</t>
         </is>
       </c>
-      <c r="L57" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L57" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>ห้องสนทนาเกิดจากการแจ้งปัญหาเท่านั้น ผู้ดูแลเปิดห้องใหม่เองไม่ได้</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ผู้ดูแลระบบพูดคุยโต้ตอบและสอบถามผู้แจ้งได้ภายในเรื่องที่แจ้ง หลักฐาน สไลด์ UAT-020 ห้องสนทนาเกิดจากการแจ้งปัญหาเท่านั้น</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4499,16 @@
           <t>ReportListPage.png</t>
         </is>
       </c>
-      <c r="L58" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M58" s="12" t="inlineStr"/>
+      <c r="L58" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ผู้ดูแลเห็นเรื่อง ผู้แจ้ง เหตุผล เวลา และรูปครบทุกช่อง ปิดเรื่องแล้วร้านค้าได้รับแจ้งเตือนผลการตรวจสอบ หลักฐาน สไลด์ UAT-020</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -4397,14 +4566,14 @@
           <t>ReportThreadDialog.png</t>
         </is>
       </c>
-      <c r="L59" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
+      <c r="L59" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>เคสเชิงลบ</t>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 เคสเชิงลบ ตอนปิดเรื่อง ผู้ดูแลแยกบันทึกภายในออกจากข้อความถึงร้าน และเลือกส่งเฉพาะข้อความถึงร้าน บันทึกภายในไม่ถูกส่งออก หลักฐาน สไลด์ UAT-020</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4633,7 @@
           <t>LoginPage.png</t>
         </is>
       </c>
-      <c r="L60" s="32" t="inlineStr">
+      <c r="L60" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -4527,12 +4696,16 @@
           <t>PendingStoresPage.png</t>
         </is>
       </c>
-      <c r="L61" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M61" s="8" t="inlineStr"/>
+      <c r="L61" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M61" s="8" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ร้านทดสอบรออนุมัติเปลี่ยนเป็น อนุมัติแล้ว พร้อมแจ้งเตือน ลงขายได้ และร้านขึ้นบนแผนที่ฝั่งลูกค้า กรณีไม่อนุมัติ ร้านได้รับข้อความแจ้งสาเหตุและยังลงขายไม่ได้ หลักฐาน สไลด์ UAT-018</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -4590,12 +4763,16 @@
           <t>StoreListPage.png</t>
         </is>
       </c>
-      <c r="L62" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M62" s="8" t="inlineStr"/>
+      <c r="L62" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 ระงับร้านทดสอบรออนุมัติพร้อมเหตุผล ร้านขึ้นสถานะ ถูกระงับ โพสต์กำลังขายเป็น 0 ฝั่งลูกค้าค้นหาชื่อร้านไม่พบและรายการอาหารไม่แสดง หลักฐาน สไลด์ UAT-021</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -4653,7 +4830,7 @@
           <t>StoreListPage.png</t>
         </is>
       </c>
-      <c r="L63" s="32" t="inlineStr">
+      <c r="L63" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -4720,7 +4897,7 @@
           <t>CustomerListPage.png</t>
         </is>
       </c>
-      <c r="L64" s="32" t="inlineStr">
+      <c r="L64" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -4783,12 +4960,16 @@
           <t>DashboardPage.png</t>
         </is>
       </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M65" s="8" t="inlineStr"/>
+      <c r="L65" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 แดชบอร์ดรวมตัวชี้วัด 10 ตัว กราฟยอดจองย้อนหลัง 7 วัน และสัดส่วนสถานะการจอง ทุกการ์ดกดเข้าไปดูรายการจริงเบื้องหลังได้ หลักฐาน สไลด์ UAT-019</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -4846,7 +5027,7 @@
           <t>PostListPage.png</t>
         </is>
       </c>
-      <c r="L66" s="32" t="inlineStr">
+      <c r="L66" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -4909,12 +5090,16 @@
           <t>ReservationListPage.png</t>
         </is>
       </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>ต้องตรวจ</t>
-        </is>
-      </c>
-      <c r="M67" s="8" t="inlineStr"/>
+      <c r="L67" s="44" t="inlineStr">
+        <is>
+          <t>ทำได้</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>ทดสอบเมื่อ 16 ก.ย. 2569 หน้าผู้ดูแลแสดงรหัสจอง ลูกค้า อาหารและร้าน ยอดเงิน ช่วงเวลารับ และสถานะ ตรงกับรายการจองในแอปลูกค้าหลายบัญชี หลักฐาน สไลด์ UAT-017</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -4972,7 +5157,7 @@
           <t>ReviewListPage.png</t>
         </is>
       </c>
-      <c r="L68" s="32" t="inlineStr">
+      <c r="L68" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5035,7 +5220,7 @@
           <t>BehaviorPage.png</t>
         </is>
       </c>
-      <c r="L69" s="32" t="inlineStr">
+      <c r="L69" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5098,7 +5283,7 @@
           <t>BehaviorPage.png</t>
         </is>
       </c>
-      <c r="L70" s="32" t="inlineStr">
+      <c r="L70" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5161,7 +5346,7 @@
           <t>BehaviorPage.png</t>
         </is>
       </c>
-      <c r="L71" s="32" t="inlineStr">
+      <c r="L71" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5224,7 +5409,7 @@
           <t>BehaviorPage.png</t>
         </is>
       </c>
-      <c r="L72" s="32" t="inlineStr">
+      <c r="L72" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5283,7 +5468,7 @@
         </is>
       </c>
       <c r="K73" s="36" t="inlineStr"/>
-      <c r="L73" s="32" t="inlineStr">
+      <c r="L73" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5346,7 +5531,7 @@
         </is>
       </c>
       <c r="K74" s="36" t="inlineStr"/>
-      <c r="L74" s="32" t="inlineStr">
+      <c r="L74" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5409,7 +5594,7 @@
         </is>
       </c>
       <c r="K75" s="36" t="inlineStr"/>
-      <c r="L75" s="32" t="inlineStr">
+      <c r="L75" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5472,7 +5657,7 @@
         </is>
       </c>
       <c r="K76" s="36" t="inlineStr"/>
-      <c r="L76" s="32" t="inlineStr">
+      <c r="L76" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5535,7 +5720,7 @@
         </is>
       </c>
       <c r="K77" s="36" t="inlineStr"/>
-      <c r="L77" s="32" t="inlineStr">
+      <c r="L77" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5598,7 +5783,7 @@
         </is>
       </c>
       <c r="K78" s="36" t="inlineStr"/>
-      <c r="L78" s="32" t="inlineStr">
+      <c r="L78" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5661,7 +5846,7 @@
         </is>
       </c>
       <c r="K79" s="36" t="inlineStr"/>
-      <c r="L79" s="32" t="inlineStr">
+      <c r="L79" s="46" t="inlineStr">
         <is>
           <t>ต้องตรวจ</t>
         </is>
@@ -5670,6 +5855,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M79"/>
+  <conditionalFormatting sqref="L2:L79">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"ทำได้"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"ทำได้บางส่วน"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"ต้องตรวจ"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5798,7 +5994,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -5848,7 +6044,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="J5" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -5898,7 +6094,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -5948,7 +6144,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J7" s="34" t="inlineStr">
+      <c r="J7" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -5998,7 +6194,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J8" s="34" t="inlineStr">
+      <c r="J8" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -6048,7 +6244,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J9" s="34" t="inlineStr">
+      <c r="J9" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -6098,7 +6294,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J10" s="34" t="inlineStr">
+      <c r="J10" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -6148,7 +6344,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="48" t="inlineStr">
         <is>
           <t>ผ่านบางส่วน</t>
         </is>
@@ -6198,7 +6394,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J12" s="34" t="inlineStr">
+      <c r="J12" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -6248,7 +6444,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J13" s="34" t="inlineStr">
+      <c r="J13" s="47" t="inlineStr">
         <is>
           <t>ผ่าน</t>
         </is>
@@ -6298,7 +6494,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J14" s="48" t="inlineStr">
         <is>
           <t>ผ่านบางส่วน</t>
         </is>
@@ -6348,7 +6544,7 @@
           <t>16 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="49" t="inlineStr">
         <is>
           <t>ยังไม่ครบ</t>
         </is>
@@ -6393,8 +6589,16 @@
           <t>UAT-013</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J16" s="48" t="inlineStr">
+        <is>
+          <t>ผ่านบางส่วน</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -6435,8 +6639,16 @@
           <t>UAT-014</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J17" s="47" t="inlineStr">
+        <is>
+          <t>ผ่าน</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -6477,8 +6689,16 @@
           <t>UAT-015</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr"/>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J18" s="47" t="inlineStr">
+        <is>
+          <t>ผ่าน</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -6519,8 +6739,16 @@
           <t>UAT-016</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr"/>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J19" s="47" t="inlineStr">
+        <is>
+          <t>ผ่าน</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -6561,8 +6789,16 @@
           <t>UAT-017</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr"/>
-      <c r="J20" s="19" t="inlineStr"/>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J20" s="48" t="inlineStr">
+        <is>
+          <t>ผ่านบางส่วน</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -6603,8 +6839,16 @@
           <t>UAT-018</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr"/>
-      <c r="J21" s="19" t="inlineStr"/>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J21" s="48" t="inlineStr">
+        <is>
+          <t>ผ่านบางส่วน</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -6645,8 +6889,16 @@
           <t>UAT-019</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr"/>
-      <c r="J22" s="19" t="inlineStr"/>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J22" s="47" t="inlineStr">
+        <is>
+          <t>ผ่าน</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
@@ -6687,8 +6939,16 @@
           <t>UAT-020</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr"/>
-      <c r="J23" s="19" t="inlineStr"/>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J23" s="48" t="inlineStr">
+        <is>
+          <t>ผ่านบางส่วน</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
@@ -6729,8 +6989,16 @@
           <t>UAT-021</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr"/>
-      <c r="J24" s="19" t="inlineStr"/>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>16 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="J24" s="48" t="inlineStr">
+        <is>
+          <t>ผ่านบางส่วน</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -6772,7 +7040,7 @@
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr"/>
-      <c r="J25" s="19" t="inlineStr"/>
+      <c r="J25" s="50" t="inlineStr"/>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="39" t="inlineStr">
@@ -6824,7 +7092,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" s="27" t="inlineStr">
         <is>
@@ -6868,6 +7135,17 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="J4:J26">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"ผ่าน"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"ผ่านบางส่วน"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
+      <formula>"ยังไม่ครบ"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
